--- a/dataset.xlsx
+++ b/dataset.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I57"/>
+  <dimension ref="A1:I89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2993,6 +2993,1446 @@
       <c r="I57" t="inlineStr">
         <is>
           <t>46. Дни недели.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="inlineStr">
+        <is>
+          <t>sound_0000056.mp3</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Цал сахаты у?</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Который час?</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>ose</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>iron</t>
+        </is>
+      </c>
+      <c r="H58" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>47. Час.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="inlineStr">
+        <is>
+          <t>sound_0000057.mp3</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Ныртӕккӕ у…</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Сейчас…</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>ose</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>iron</t>
+        </is>
+      </c>
+      <c r="H59" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>47. Час.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="inlineStr">
+        <is>
+          <t>sound_0000058.mp3</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>ӕртӕ сахаты.</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>три часа</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>ose</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>iron</t>
+        </is>
+      </c>
+      <c r="H60" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>47. Час.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="inlineStr">
+        <is>
+          <t>sound_0000059.mp3</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>боны дыууӕ сахатыл.</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>в два часа дня.</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>ose</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>iron</t>
+        </is>
+      </c>
+      <c r="H61" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>47. Час.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="inlineStr">
+        <is>
+          <t>sound_0000060.mp3</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>ӕхсӕвы ӕртӕ сахатыл.</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>в три часа ночи.</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>ose</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>iron</t>
+        </is>
+      </c>
+      <c r="H62" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>47. Час.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="inlineStr">
+        <is>
+          <t>sound_0000061.mp3</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>дӕсӕм ӕрдӕгыл.</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>в половине десятого.</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>ose</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>iron</t>
+        </is>
+      </c>
+      <c r="H63" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>47. Час.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="inlineStr">
+        <is>
+          <t>sound_0000062.mp3</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>фарӕстӕм ӕрдӕгыл.</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>в половине девятого.</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>ose</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>iron</t>
+        </is>
+      </c>
+      <c r="H64" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>47. Час.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="1" t="inlineStr">
+        <is>
+          <t>sound_0000063.mp3</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Фынддӕс минуты мӕм банхъӕлмӕ кӕс.</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Подожди меня пятнадцать минут.</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>ose</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>iron</t>
+        </is>
+      </c>
+      <c r="H65" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>47. Час.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="1" t="inlineStr">
+        <is>
+          <t>sound_0000064.mp3</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Сахаты ʼрдӕг мӕм банхъӕлмӕ кӕс.</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Подожди меня полчаса.</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>ose</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>iron</t>
+        </is>
+      </c>
+      <c r="H66" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>47. Час.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="1" t="inlineStr">
+        <is>
+          <t>sound_0000065.mp3</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Мӕнӕн рӕстӕг нал ис.</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>У меня уже нет времени.</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>ose</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>iron</t>
+        </is>
+      </c>
+      <c r="H67" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>47. Час.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="1" t="inlineStr">
+        <is>
+          <t>sound_0000066.mp3</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Ӕрбахӕццӕ кӕны январь.</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Приближается январь.</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>ose</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>iron</t>
+        </is>
+      </c>
+      <c r="H68" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>48. Месяцы.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="1" t="inlineStr">
+        <is>
+          <t>sound_0000067.mp3</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Уый уыдзӕн мӕйы фӕстӕ.</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Это будет через месяц.</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>ose</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>iron</t>
+        </is>
+      </c>
+      <c r="H69" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>48. Месяцы.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="1" t="inlineStr">
+        <is>
+          <t>sound_0000068.mp3</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Мӕ отпуск уыдзӕни мӕй ӕмӕ ӕрджӕджы фӕстӕ.</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Отпуск у меня будет через полтора месяца.</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>ose</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>iron</t>
+        </is>
+      </c>
+      <c r="H70" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>48. Месяцы.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="1" t="inlineStr">
+        <is>
+          <t>sound_0000069.mp3</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Кӕд уӕм райдайынц…</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Когда у вас начинают...</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>ose</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>iron</t>
+        </is>
+      </c>
+      <c r="H71" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>48. Месяцы.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="1" t="inlineStr">
+        <is>
+          <t>sound_0000070.mp3</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Кӕд уӕм сцӕттӕ вӕййы…</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Когда у вас поспевает…</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>ose</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>iron</t>
+        </is>
+      </c>
+      <c r="H72" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>48. Месяцы.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="1" t="inlineStr">
+        <is>
+          <t>sound_0000071.mp3</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>мӕнӕу.</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>пшеница</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>ose</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>iron</t>
+        </is>
+      </c>
+      <c r="H73" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>48. Месяцы.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="1" t="inlineStr">
+        <is>
+          <t>sound_0000072.mp3</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Тур кмӕ.</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>в Турцию.</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>ose</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>iron</t>
+        </is>
+      </c>
+      <c r="H74" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>48. Месяцы.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="1" t="inlineStr">
+        <is>
+          <t>sound_0000073.mp3</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Цалдӕр мӕйы фӕстӕ мах хъуамӕ ӕнӕмӕнг сӕмбӕлӕм.</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Через несколько месяцев мы должны обязательно встретиться.</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>ose</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>iron</t>
+        </is>
+      </c>
+      <c r="H75" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>48. Месяцы.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="1" t="inlineStr">
+        <is>
+          <t>sound_0000074.mp3</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Абон цалӕм у?</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Какое сегодня число?</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>ose</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>iron</t>
+        </is>
+      </c>
+      <c r="H76" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>48. Месяцы.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="1" t="inlineStr">
+        <is>
+          <t>sound_0000075.mp3</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Абон цавӕр рӕстӕг у?</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Какая сегодня погода?</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>ose</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>iron</t>
+        </is>
+      </c>
+      <c r="H77" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>49. Погода.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="1" t="inlineStr">
+        <is>
+          <t>sound_0000076.mp3</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Абон хорз бон скодта.</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Сегодня хорошая погода.</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>ose</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>iron</t>
+        </is>
+      </c>
+      <c r="H78" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>49. Погода.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="1" t="inlineStr">
+        <is>
+          <t>sound_0000077.mp3</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Абон ӕвзӕр бон скодта.</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Сегодня плохая погода.</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>ose</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>iron</t>
+        </is>
+      </c>
+      <c r="H79" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>49. Погода.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="1" t="inlineStr">
+        <is>
+          <t>sound_0000078.mp3</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>уазал бон у.</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>холодно.</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>ose</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>iron</t>
+        </is>
+      </c>
+      <c r="H80" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>49. Погода.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="1" t="inlineStr">
+        <is>
+          <t>sound_0000079.mp3</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>мигъ бон у.</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>туман.</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>ose</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>iron</t>
+        </is>
+      </c>
+      <c r="H81" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>49. Погода.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="1" t="inlineStr">
+        <is>
+          <t>sound_0000080.mp3</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>дымгӕ бон у.</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>ветер.</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>ose</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>iron</t>
+        </is>
+      </c>
+      <c r="H82" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>49. Погода.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="1" t="inlineStr">
+        <is>
+          <t>sound_0000081.mp3</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Рӕстӕджы сводкӕмӕ хъуыстай?</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Ты слушал сводку о погоде?</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>ose</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>iron</t>
+        </is>
+      </c>
+      <c r="H83" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>49. Погода.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="1" t="inlineStr">
+        <is>
+          <t>sound_0000082.mp3</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Цавӕр рӕстӕг уыдзӕн райсом?</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Какая завтра будет погода?</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>ose</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>iron</t>
+        </is>
+      </c>
+      <c r="H84" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>49. Погода.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="1" t="inlineStr">
+        <is>
+          <t>sound_0000083.mp3</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Райсом уыдзӕни…</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Завтра будет…</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>ose</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>iron</t>
+        </is>
+      </c>
+      <c r="H85" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>49. Погода.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="1" t="inlineStr">
+        <is>
+          <t>sound_0000084.mp3</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>мит.</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>снег.</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>ose</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>iron</t>
+        </is>
+      </c>
+      <c r="H86" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>49. Погода.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="1" t="inlineStr">
+        <is>
+          <t>sound_0000085.mp3</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>дыууын аст градусы хъарм.</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>двадцать восемь градусов тепла.</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>ose</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>iron</t>
+        </is>
+      </c>
+      <c r="H87" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>49. Погода.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="1" t="inlineStr">
+        <is>
+          <t>sound_0000086.mp3</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Абон цы диссаджы бон скодта!</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Какая сегодня чудесная погода!</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>ose</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>iron</t>
+        </is>
+      </c>
+      <c r="H88" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>49. Погода.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="1" t="inlineStr">
+        <is>
+          <t>sound_0000087.mp3</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Рӕстӕг хӕхты ивга у.</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Погода в горах изменчива.</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>ose</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>iron</t>
+        </is>
+      </c>
+      <c r="H89" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>49. Погода.pdf</t>
         </is>
       </c>
     </row>
@@ -3053,6 +4493,38 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A55" r:id="rId53"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A56" r:id="rId54"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A57" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A58" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A59" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A60" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A61" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A62" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A63" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A64" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A65" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A66" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A67" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A68" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A69" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A70" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A71" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A72" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A73" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A74" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A75" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A76" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A77" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A78" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A79" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A80" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A81" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A82" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A83" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A84" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A85" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A86" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A87" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A88" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A89" r:id="rId87"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dataset.xlsx
+++ b/dataset.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I89"/>
+  <dimension ref="A1:I140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -4433,6 +4433,2301 @@
       <c r="I89" t="inlineStr">
         <is>
           <t>49. Погода.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="1" t="inlineStr">
+        <is>
+          <t>sound_0000088.mp3</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Ӕз фыццаг хатт дӕн сымах горӕты.</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Я первый раз в вашем городе.</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>ose</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>iron</t>
+        </is>
+      </c>
+      <c r="H90" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>50. Ч. 1. В городе, в селе.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="1" t="inlineStr">
+        <is>
+          <t>sound_0000089.mp3</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Мах фыццаг хатт стӕм сымах хъӕуы.</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Мы первый раз в вашем селе.</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>ose</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>iron</t>
+        </is>
+      </c>
+      <c r="H91" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>50. Ч. 1. В городе, в селе.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="1" t="inlineStr">
+        <is>
+          <t>sound_0000090.mp3</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Мӕ зӕрдӕмӕ тынг фӕцыди уӕ горӕт.</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Мне очень понравился ваш город.</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>ose</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>iron</t>
+        </is>
+      </c>
+      <c r="H92" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>50. Ч. 1. В городе, в селе.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="1" t="inlineStr">
+        <is>
+          <t>sound_0000091.mp3</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Цы фенӕн ис уӕ горӕты.</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Что можно посмотреть в вашем городе?</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>ose</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>iron</t>
+        </is>
+      </c>
+      <c r="H93" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>50. Ч. 1. В городе, в селе.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="1" t="inlineStr">
+        <is>
+          <t>sound_0000092.mp3</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Кӕм ис ам</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Где здесь</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>ose</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>iron</t>
+        </is>
+      </c>
+      <c r="H94" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>50. Ч. 1. В городе, в селе.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="1" t="inlineStr">
+        <is>
+          <t>sound_0000093.mp3</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>вокзал?</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>вокзал?</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>ose</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>iron</t>
+        </is>
+      </c>
+      <c r="H95" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>50. Ч. 1. В городе, в селе.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="1" t="inlineStr">
+        <is>
+          <t>sound_0000094.mp3</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>почтӕ?</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>почта?</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>ose</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>iron</t>
+        </is>
+      </c>
+      <c r="H96" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>50. Ч. 1. В городе, в селе.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="1" t="inlineStr">
+        <is>
+          <t>sound_0000095.mp3</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Дӕ хорзӕхӕй, тагъддӕр цу!</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Поезжай, пожалуйста, быстрей!</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>ose</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>iron</t>
+        </is>
+      </c>
+      <c r="H97" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>50. Ч. 1. В городе, в селе.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="1" t="inlineStr">
+        <is>
+          <t>sound_0000096.mp3</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Бауром машинӕ.</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Останови машину.</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>ose</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>iron</t>
+        </is>
+      </c>
+      <c r="H98" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>50. Ч. 1. В городе, в селе.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="1" t="inlineStr">
+        <is>
+          <t>sound_0000097.mp3</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Терк кӕлы горӕт Дзӕуджыхъӕуы астӕуты.</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Терек течет посередине города Владикавказа.</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>ose</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>iron</t>
+        </is>
+      </c>
+      <c r="H99" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>50. Ч. 1. В городе, в селе.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="1" t="inlineStr">
+        <is>
+          <t>sound_0000098.mp3</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Ӕз фӕдзӕгъӕл дӕн.</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Я заблудился.</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>ose</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>iron</t>
+        </is>
+      </c>
+      <c r="H100" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>50. Ч. 2. Заблудиться.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="1" t="inlineStr">
+        <is>
+          <t>sound_0000099.mp3</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>скъола.</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>школа.</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>ose</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>iron</t>
+        </is>
+      </c>
+      <c r="H101" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>50. Ч. 2. Заблудиться.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="1" t="inlineStr">
+        <is>
+          <t>sound_0000100.mp3</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>дук ани.</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>магазин.</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>ose</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>iron</t>
+        </is>
+      </c>
+      <c r="H102" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>50. Ч. 2. Заблудиться.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="1" t="inlineStr">
+        <is>
+          <t>sound_0000101.mp3</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Ӕз ардыгон нӕ дӕн, амы бынӕттӕ нӕ зонын.</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Я нездешний, не знаю местности.</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>ose</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>iron</t>
+        </is>
+      </c>
+      <c r="H103" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>50. Ч. 2. Заблудиться.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="1" t="inlineStr">
+        <is>
+          <t>sound_0000102.mp3</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Ацы хидыл бацӕуын тӕссаг нӕу?</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Не опасно ли пройти по этому мосту?</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>ose</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>iron</t>
+        </is>
+      </c>
+      <c r="H104" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>50. Ч. 3. Мост.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="1" t="inlineStr">
+        <is>
+          <t>sound_0000103.mp3</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Ӕз нӕ уӕн дын ацы хидыл цӕуын.</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Я боюсь идти по этому мосту.</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>ose</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>iron</t>
+        </is>
+      </c>
+      <c r="H105" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>50. Ч. 3. Мост.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="1" t="inlineStr">
+        <is>
+          <t>sound_0000104.mp3</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Фех хуыс-ма мын кӕн фаллаг фарсмӕ бахизынмӕ.</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Помоги мне перебраться на ту сторону.</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>ose</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>iron</t>
+        </is>
+      </c>
+      <c r="H106" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>50. Ч. 3. Мост.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="1" t="inlineStr">
+        <is>
+          <t>sound_0000105.mp3</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Ам хид саразын хъӕуы.</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Здесь надо построить мост.</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>ose</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>iron</t>
+        </is>
+      </c>
+      <c r="H107" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>50. Ч. 3. Мост.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="1" t="inlineStr">
+        <is>
+          <t>sound_0000106.mp3</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Цал адӕймаджы цӕры уӕ горӕты?</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Сколько человек проживает в вашем городе?</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>ose</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>iron</t>
+        </is>
+      </c>
+      <c r="H108" t="n">
+        <v>3</v>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>50. Ч. 4. Население.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="1" t="inlineStr">
+        <is>
+          <t>sound_0000107.mp3</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Цавӕр адӕмы хӕттытӕ уӕм цӕры?</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Люди каких национальностей живут у вас?</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>ose</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>iron</t>
+        </is>
+      </c>
+      <c r="H109" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>50. Ч. 4. Население.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="1" t="inlineStr">
+        <is>
+          <t>sound_0000108.mp3</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Махмӕ цӕрынц…</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>У нас живут…</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>ose</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>iron</t>
+        </is>
+      </c>
+      <c r="H110" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>50. Ч. 4. Население.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="1" t="inlineStr">
+        <is>
+          <t>sound_0000109.mp3</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Мах хъӕуы цӕрынц… уырыссӕгтӕ, украинӕгтӕ, ирӕттӕ, гуырдзиӕгтӕ, сомихӕгтӕ ӕмӕ ӕндӕр адӕмы хӕттытӕ.</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>В нашем селе живут… русские, украинцы, осетины, грузины, армяне и люди других национальностей.</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>ose</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>iron</t>
+        </is>
+      </c>
+      <c r="H111" t="n">
+        <v>11.38</v>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>50. Ч. 4. Население.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="1" t="inlineStr">
+        <is>
+          <t>sound_0000110.mp3</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Ацы цырт кӕмӕн ӕвӕрд у?</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Кому поставлен этот памятник?</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>ose</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>iron</t>
+        </is>
+      </c>
+      <c r="H112" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>50. Ч. 5. Памятник.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="1" t="inlineStr">
+        <is>
+          <t>sound_0000111.mp3</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Мӕн фӕнды инӕлар Плийы-фырты цырт фенын.</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Я хочу посмотреть памятник генералу Плиеву.</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>ose</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>iron</t>
+        </is>
+      </c>
+      <c r="H113" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>50. Ч. 5. Памятник.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="1" t="inlineStr">
+        <is>
+          <t>sound_0000112.mp3</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Кӕд ӕрцыд ӕвӕрд ацы цырт?</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Когда был поставлен этот памятник?</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>ose</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>iron</t>
+        </is>
+      </c>
+      <c r="H114" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>50. Ч. 5. Памятник.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="1" t="inlineStr">
+        <is>
+          <t>sound_0000113.mp3</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Ӕфсымӕрон ингӕн кӕцы ран ис?</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Где братская могила?</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>ose</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>iron</t>
+        </is>
+      </c>
+      <c r="H115" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>50. Ч. 5. Памятник.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="1" t="inlineStr">
+        <is>
+          <t>sound_0000114.mp3</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Ӕфсымӕрон ингӕнмӕ-ма мӕ схӕццӕ кӕн.</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Проведи меня до братской могилы.</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>ose</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>iron</t>
+        </is>
+      </c>
+      <c r="H116" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>50. Ч. 5. Памятник.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="1" t="inlineStr">
+        <is>
+          <t>sound_0000115.mp3</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Цал адӕймаджы ныгӕд дзы ис?</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Сколько человек там похоронено?</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>ose</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>iron</t>
+        </is>
+      </c>
+      <c r="H117" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>50. Ч. 5. Памятник.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="1" t="inlineStr">
+        <is>
+          <t>sound_0000116.mp3</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Ацы ʼфсымӕрон ингӕны ныгӕд ис ӕвддӕс мин адӕймаджы.</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>В этой братской могиле похоронено 17 тысяч человек.</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>ose</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>iron</t>
+        </is>
+      </c>
+      <c r="H118" t="n">
+        <v>12.18</v>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>50. Ч. 5. Памятник.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="1" t="inlineStr">
+        <is>
+          <t>sound_0000117.mp3</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Хетӕгкаты Къостайы цырт мӕ зӕрдӕмӕ тынг цӕуы.</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Мне очень нравиться памятник Коста Хетагурову.</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>ose</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>iron</t>
+        </is>
+      </c>
+      <c r="H119" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>50. Ч. 5. Памятник.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="1" t="inlineStr">
+        <is>
+          <t>sound_0000118.mp3</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Уӕ горӕты парк ис?</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Есть ли у вас в городе парк?</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>ose</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>iron</t>
+        </is>
+      </c>
+      <c r="H120" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>50. Ч. 6. Парк.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="1" t="inlineStr">
+        <is>
+          <t>sound_0000119.mp3</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Цомут паркмӕ.</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Пойдемте в парк.</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>ose</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>iron</t>
+        </is>
+      </c>
+      <c r="H121" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>50. Ч. 6. Парк.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="1" t="inlineStr">
+        <is>
+          <t>sound_0000120.mp3</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Дӕ зӕрдӕмӕ цӕуы нӕ парк?</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Нравится тебе наш парк?</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>ose</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>iron</t>
+        </is>
+      </c>
+      <c r="H122" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>50. Ч. 6. Парк.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="1" t="inlineStr">
+        <is>
+          <t>sound_0000121.mp3</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Фыццаг хатт дӕ ацы парчы?</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Ты первый раз в этом парке?</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>ose</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>iron</t>
+        </is>
+      </c>
+      <c r="H123" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>50. Ч. 6. Парк.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="1" t="inlineStr">
+        <is>
+          <t>sound_0000122.mp3</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Абадӕм ам бандоныл.</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Посидим здесь на скамейке.</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>ose</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>iron</t>
+        </is>
+      </c>
+      <c r="H124" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>50. Ч. 6. Парк.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="1" t="inlineStr">
+        <is>
+          <t>sound_0000123.mp3</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Цы бӕрзонд бӕлас у!</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Какое высокое дерево!</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>ose</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>iron</t>
+        </is>
+      </c>
+      <c r="H125" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>50. Ч. 6. Парк.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="1" t="inlineStr">
+        <is>
+          <t>sound_0000124.mp3</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Цом ацы аллейӕйыл.</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Пойдем по этой аллее.</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>ose</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>iron</t>
+        </is>
+      </c>
+      <c r="H126" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>50. Ч. 6. Парк.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="1" t="inlineStr">
+        <is>
+          <t>sound_0000125.mp3</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Фӕскомцӕдисон парк кӕм и?</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Где находится Комсомольский парк?</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>ose</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>iron</t>
+        </is>
+      </c>
+      <c r="H127" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>50. Ч. 6. Парк.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="1" t="inlineStr">
+        <is>
+          <t>sound_0000126.mp3</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Горӕты сӕйраг фӕзы ном куыд у?</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Как называется центральная площадь города?</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>ose</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>iron</t>
+        </is>
+      </c>
+      <c r="H128" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>50. Ч. 7. Площадь.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="1" t="inlineStr">
+        <is>
+          <t>sound_0000127.mp3</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Ацы фӕзы ном куыд у?</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Как эта площадь называется?</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>ose</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>iron</t>
+        </is>
+      </c>
+      <c r="H129" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>50. Ч. 7. Площадь.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="1" t="inlineStr">
+        <is>
+          <t>sound_0000128.mp3</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Ленины фӕзмӕ-ма мӕ схӕццӕ кӕн.</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Проводи меня до площади Ленина.</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>ose</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>iron</t>
+        </is>
+      </c>
+      <c r="H130" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>50. Ч. 7. Площадь.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="1" t="inlineStr">
+        <is>
+          <t>sound_0000129.mp3</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Уӕ горӕты базар ис?</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Есть ли у вас в городе базар?</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>ose</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>iron</t>
+        </is>
+      </c>
+      <c r="H131" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>50. Ч. 8. Рынок.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="1" t="inlineStr">
+        <is>
+          <t>sound_0000130.mp3</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Дард у базар?</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Далеко ли до рынка?</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>ose</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>iron</t>
+        </is>
+      </c>
+      <c r="H132" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>50. Ч. 8. Рынок.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="1" t="inlineStr">
+        <is>
+          <t>sound_0000131.mp3</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Кӕм ис ам…</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Где здесь…</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>ose</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>iron</t>
+        </is>
+      </c>
+      <c r="H133" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>50. Ч. 8. Рынок.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="1" t="inlineStr">
+        <is>
+          <t>sound_0000132.mp3</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>фыды павильон?</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>мясной павильон?</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>ose</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>iron</t>
+        </is>
+      </c>
+      <c r="H134" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>50. Ч. 8. Рынок.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="1" t="inlineStr">
+        <is>
+          <t>sound_0000133.mp3</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Кӕм ис Пушкины уынг?</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Где находится улица Пушкина?</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>ose</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>iron</t>
+        </is>
+      </c>
+      <c r="H135" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>50. Ч. 9. Улица.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="1" t="inlineStr">
+        <is>
+          <t>sound_0000134.mp3</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Кӕм ис Хетӕгкаты Къостайы уынг?</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Где находится улица</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>ose</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>iron</t>
+        </is>
+      </c>
+      <c r="H136" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>50. Ч. 9. Улица.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="1" t="inlineStr">
+        <is>
+          <t>sound_0000135.mp3</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Кӕм ис сӕйраг уынг?</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Где главная улица?</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>ose</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>iron</t>
+        </is>
+      </c>
+      <c r="H137" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>50. Ч. 9. Улица.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="1" t="inlineStr">
+        <is>
+          <t>sound_0000136.mp3</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Куыд у ацы уынджы ном?</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Как называется эта улица?</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>ose</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>iron</t>
+        </is>
+      </c>
+      <c r="H138" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>50. Ч. 9. Улица.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="1" t="inlineStr">
+        <is>
+          <t>sound_0000137.mp3</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Мӕнӕ ацы уынгыл цом.</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Пойдемте по этой улице.</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>ose</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>iron</t>
+        </is>
+      </c>
+      <c r="H139" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>50. Ч. 9. Улица.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="1" t="inlineStr">
+        <is>
+          <t>sound_0000138.mp3</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Цы бирӕ ног хӕдзӕрттӕ ис ацы уынджы!</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Как много новых домов по этой улице!</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>ose</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>iron</t>
+        </is>
+      </c>
+      <c r="H140" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>50. Ч. 9. Улица.pdf</t>
         </is>
       </c>
     </row>
@@ -4525,6 +6820,57 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A87" r:id="rId85"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A88" r:id="rId86"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A89" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A90" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A91" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A92" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A93" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A94" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A95" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A96" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A97" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A98" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A99" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A100" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A101" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A102" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A103" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A104" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A105" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A106" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A107" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A108" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A109" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A110" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A111" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A112" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A113" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A114" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A115" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A116" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A117" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A118" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A119" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A120" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A121" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A122" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A123" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A124" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A125" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A126" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A127" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A128" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A129" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A130" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A131" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A132" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A133" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A134" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A135" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A136" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A137" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A138" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A139" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A140" r:id="rId138"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
